--- a/MathTechPy/data/ExamA01Score.xlsx
+++ b/MathTechPy/data/ExamA01Score.xlsx
@@ -16803,133 +16803,133 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.6</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>4.9</v>
+        <v>23.3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8</v>
+        <v>36.3</v>
       </c>
       <c r="E2" t="n">
         <v>12.2</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>22.2</v>
       </c>
       <c r="G2" t="n">
         <v>12.5</v>
       </c>
       <c r="H2" t="n">
-        <v>10.8</v>
+        <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>34.8</v>
       </c>
       <c r="J2" t="n">
-        <v>8.1</v>
+        <v>38.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>23.2</v>
       </c>
       <c r="L2" t="n">
         <v>17.9</v>
       </c>
       <c r="M2" t="n">
-        <v>11.6</v>
+        <v>35.9</v>
       </c>
       <c r="N2" t="n">
         <v>20.8</v>
       </c>
       <c r="O2" t="n">
-        <v>10.4</v>
+        <v>29.1</v>
       </c>
       <c r="P2" t="n">
-        <v>9.800000000000001</v>
+        <v>28.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.7</v>
+        <v>43.9</v>
       </c>
       <c r="R2" t="n">
-        <v>8.300000000000001</v>
+        <v>26</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.9</v>
+        <v>34.7</v>
       </c>
       <c r="U2" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="V2" t="n">
-        <v>6.8</v>
+        <v>31.9</v>
       </c>
       <c r="W2" t="n">
         <v>15</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>28.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.6</v>
+        <v>34</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.4</v>
+        <v>38.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.300000000000001</v>
+        <v>34.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.5</v>
+        <v>37.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.2</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>37.1</v>
       </c>
       <c r="AE2" t="n">
         <v>9.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.5</v>
+        <v>34.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2</v>
+        <v>35.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>5.9</v>
+        <v>32.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.7</v>
+        <v>23.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.5</v>
+        <v>29.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>8.6</v>
+        <v>40.7</v>
       </c>
       <c r="AL2" t="n">
         <v>14.7</v>
       </c>
       <c r="AM2" t="n">
-        <v>9.199999999999999</v>
+        <v>40.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.8</v>
+        <v>44.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="AP2" t="n">
         <v>12.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.9</v>
+        <v>37</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>44.5</v>
       </c>
       <c r="AS2" t="n">
         <v>15.3</v>
@@ -16941,106 +16941,106 @@
         <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.2</v>
+        <v>33.3</v>
       </c>
       <c r="AW2" t="n">
         <v>13.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.6</v>
+        <v>35</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>53.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.9</v>
+        <v>33.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.7</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.4</v>
+        <v>39.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.8</v>
+        <v>35.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.3</v>
+        <v>25.7</v>
       </c>
       <c r="BE2" t="n">
         <v>13</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.800000000000001</v>
+        <v>30.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>29.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.3</v>
+        <v>22.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>13</v>
+        <v>37.4</v>
       </c>
       <c r="BJ2" t="n">
         <v>14</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>28.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>8.4</v>
+        <v>22.8</v>
       </c>
       <c r="BM2" t="n">
         <v>12.2</v>
       </c>
       <c r="BN2" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BO2" t="n">
-        <v>6.2</v>
+        <v>30.8</v>
       </c>
       <c r="BP2" t="n">
         <v>15</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.3</v>
+        <v>47.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="BS2" t="n">
-        <v>13.6</v>
+        <v>38.1</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.5</v>
+        <v>40</v>
       </c>
       <c r="BU2" t="n">
         <v>13.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.2</v>
+        <v>31.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.7</v>
+        <v>29.9</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.5</v>
+        <v>24.2</v>
       </c>
       <c r="BY2" t="n">
         <v>12.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.1</v>
+        <v>38.1</v>
       </c>
       <c r="CA2" t="n">
         <v>12.1</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.8</v>
+        <v>25.8</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.4</v>
+        <v>36.6</v>
       </c>
       <c r="CD2" t="n">
         <v>10.7</v>
@@ -17049,58 +17049,58 @@
         <v>12.5</v>
       </c>
       <c r="CF2" t="n">
-        <v>6.6</v>
+        <v>50</v>
       </c>
       <c r="CG2" t="n">
-        <v>4.9</v>
+        <v>39.8</v>
       </c>
       <c r="CH2" t="n">
         <v>14.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>7.6</v>
+        <v>38.1</v>
       </c>
       <c r="CJ2" t="n">
-        <v>3.1</v>
+        <v>31.9</v>
       </c>
       <c r="CK2" t="n">
-        <v>9.199999999999999</v>
+        <v>42.6</v>
       </c>
       <c r="CL2" t="n">
-        <v>6.2</v>
+        <v>35.5</v>
       </c>
       <c r="CM2" t="n">
-        <v>11.4</v>
+        <v>41.6</v>
       </c>
       <c r="CN2" t="n">
         <v>14.3</v>
       </c>
       <c r="CO2" t="n">
-        <v>8.5</v>
+        <v>23.4</v>
       </c>
       <c r="CP2" t="n">
-        <v>6.1</v>
+        <v>27.8</v>
       </c>
       <c r="CQ2" t="n">
-        <v>10.7</v>
+        <v>28.4</v>
       </c>
       <c r="CR2" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.6</v>
+        <v>42.6</v>
       </c>
       <c r="CT2" t="n">
         <v>12.7</v>
       </c>
       <c r="CU2" t="n">
-        <v>7.1</v>
+        <v>38.8</v>
       </c>
       <c r="CV2" t="n">
-        <v>8.9</v>
+        <v>34.3</v>
       </c>
       <c r="CW2" t="n">
-        <v>11.1</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="3">
@@ -17790,7 +17790,7 @@
         <v>30.7</v>
       </c>
       <c r="X5" t="n">
-        <v>17.6</v>
+        <v>50.9</v>
       </c>
       <c r="Y5" t="n">
         <v>27.6</v>
@@ -17799,7 +17799,7 @@
         <v>31.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.2</v>
+        <v>59.3</v>
       </c>
       <c r="AB5" t="n">
         <v>23.1</v>
@@ -18070,7 +18070,7 @@
         <v>22.5</v>
       </c>
       <c r="O6" t="n">
-        <v>13.9</v>
+        <v>41.4</v>
       </c>
       <c r="P6" t="n">
         <v>16.4</v>
@@ -18097,7 +18097,7 @@
         <v>19.2</v>
       </c>
       <c r="X6" t="n">
-        <v>13.1</v>
+        <v>37.3</v>
       </c>
       <c r="Y6" t="n">
         <v>21.5</v>
@@ -18118,7 +18118,7 @@
         <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>7.8</v>
+        <v>23.2</v>
       </c>
       <c r="AF6" t="n">
         <v>16.4</v>
@@ -18175,7 +18175,7 @@
         <v>20.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.1</v>
+        <v>27</v>
       </c>
       <c r="AY6" t="n">
         <v>18.4</v>
@@ -18265,7 +18265,7 @@
         <v>20.4</v>
       </c>
       <c r="CB6" t="n">
-        <v>11.8</v>
+        <v>31.8</v>
       </c>
       <c r="CC6" t="n">
         <v>18.2</v>
@@ -18277,7 +18277,7 @@
         <v>21.2</v>
       </c>
       <c r="CF6" t="n">
-        <v>12.6</v>
+        <v>39.9</v>
       </c>
       <c r="CG6" t="n">
         <v>15.3</v>
@@ -19900,7 +19900,7 @@
         <v>26.7</v>
       </c>
       <c r="K12" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="L12" t="n">
         <v>23.5</v>
@@ -20029,7 +20029,7 @@
         <v>28.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.8</v>
+        <v>34.7</v>
       </c>
       <c r="BC12" t="n">
         <v>24.1</v>
@@ -20062,7 +20062,7 @@
         <v>15</v>
       </c>
       <c r="BM12" t="n">
-        <v>11.7</v>
+        <v>36.9</v>
       </c>
       <c r="BN12" t="n">
         <v>22.7</v>
@@ -20180,7 +20180,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.7</v>
+        <v>66</v>
       </c>
       <c r="C13" t="n">
         <v>19.8</v>
@@ -20192,13 +20192,13 @@
         <v>26.7</v>
       </c>
       <c r="F13" t="n">
-        <v>16.7</v>
+        <v>50.7</v>
       </c>
       <c r="G13" t="n">
         <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>15.4</v>
+        <v>44.3</v>
       </c>
       <c r="I13" t="n">
         <v>29.9</v>
@@ -20225,7 +20225,7 @@
         <v>21.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.8</v>
+        <v>44.7</v>
       </c>
       <c r="R13" t="n">
         <v>25.3</v>
@@ -20234,10 +20234,10 @@
         <v>23.6</v>
       </c>
       <c r="T13" t="n">
-        <v>18.2</v>
+        <v>43.7</v>
       </c>
       <c r="U13" t="n">
-        <v>15.8</v>
+        <v>52.8</v>
       </c>
       <c r="V13" t="n">
         <v>23.1</v>
@@ -20246,16 +20246,16 @@
         <v>24.8</v>
       </c>
       <c r="X13" t="n">
-        <v>17.7</v>
+        <v>59.3</v>
       </c>
       <c r="Y13" t="n">
         <v>18.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>53.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>18.3</v>
+        <v>47.3</v>
       </c>
       <c r="AB13" t="n">
         <v>22.7</v>
@@ -20267,7 +20267,7 @@
         <v>22.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>17</v>
+        <v>56.6</v>
       </c>
       <c r="AF13" t="n">
         <v>23.1</v>
@@ -20291,7 +20291,7 @@
         <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>14.4</v>
+        <v>53.9</v>
       </c>
       <c r="AN13" t="n">
         <v>25.8</v>
@@ -20315,7 +20315,7 @@
         <v>22.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>16.2</v>
+        <v>48.6</v>
       </c>
       <c r="AV13" t="n">
         <v>21.8</v>
@@ -20330,7 +20330,7 @@
         <v>27.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BA13" t="n">
         <v>18.8</v>
@@ -20357,7 +20357,7 @@
         <v>22.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>14.3</v>
+        <v>54.5</v>
       </c>
       <c r="BJ13" t="n">
         <v>28</v>
@@ -20369,7 +20369,7 @@
         <v>27.6</v>
       </c>
       <c r="BM13" t="n">
-        <v>14.5</v>
+        <v>35.5</v>
       </c>
       <c r="BN13" t="n">
         <v>20.2</v>
@@ -20384,10 +20384,10 @@
         <v>16.2</v>
       </c>
       <c r="BR13" t="n">
-        <v>14.6</v>
+        <v>52.9</v>
       </c>
       <c r="BS13" t="n">
-        <v>15.6</v>
+        <v>51.1</v>
       </c>
       <c r="BT13" t="n">
         <v>20.7</v>
@@ -20411,7 +20411,7 @@
         <v>26</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.300000000000001</v>
+        <v>55</v>
       </c>
       <c r="CB13" t="n">
         <v>17.1</v>
@@ -20441,7 +20441,7 @@
         <v>21.1</v>
       </c>
       <c r="CK13" t="n">
-        <v>16.1</v>
+        <v>43.3</v>
       </c>
       <c r="CL13" t="n">
         <v>20.5</v>
@@ -20462,10 +20462,10 @@
         <v>21.5</v>
       </c>
       <c r="CR13" t="n">
-        <v>10.1</v>
+        <v>52.6</v>
       </c>
       <c r="CS13" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="CT13" t="n">
         <v>18.5</v>
@@ -20794,7 +20794,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.7</v>
+        <v>35.9</v>
       </c>
       <c r="C15" t="n">
         <v>16.2</v>
@@ -20809,13 +20809,13 @@
         <v>26.5</v>
       </c>
       <c r="G15" t="n">
-        <v>10.7</v>
+        <v>38.1</v>
       </c>
       <c r="H15" t="n">
-        <v>11.1</v>
+        <v>47.6</v>
       </c>
       <c r="I15" t="n">
-        <v>14.4</v>
+        <v>52.3</v>
       </c>
       <c r="J15" t="n">
         <v>18.1</v>
@@ -20833,10 +20833,10 @@
         <v>18.7</v>
       </c>
       <c r="O15" t="n">
-        <v>8.300000000000001</v>
+        <v>29.8</v>
       </c>
       <c r="P15" t="n">
-        <v>9.4</v>
+        <v>41.5</v>
       </c>
       <c r="Q15" t="n">
         <v>14.6</v>
@@ -20854,13 +20854,13 @@
         <v>16.8</v>
       </c>
       <c r="V15" t="n">
-        <v>10.3</v>
+        <v>38.3</v>
       </c>
       <c r="W15" t="n">
         <v>17.4</v>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>36.5</v>
       </c>
       <c r="Y15" t="n">
         <v>15.6</v>
@@ -20878,7 +20878,7 @@
         <v>17.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.5</v>
+        <v>43.4</v>
       </c>
       <c r="AE15" t="n">
         <v>17.3</v>
@@ -20887,7 +20887,7 @@
         <v>15.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>7.2</v>
+        <v>34.5</v>
       </c>
       <c r="AH15" t="n">
         <v>15.5</v>
@@ -20896,7 +20896,7 @@
         <v>16.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>12.2</v>
+        <v>44.8</v>
       </c>
       <c r="AK15" t="n">
         <v>12</v>
@@ -20914,10 +20914,10 @@
         <v>18.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>12.8</v>
+        <v>40.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.2</v>
+        <v>33.3</v>
       </c>
       <c r="AR15" t="n">
         <v>16.6</v>
@@ -20926,10 +20926,10 @@
         <v>18.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.800000000000001</v>
+        <v>33.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>12.6</v>
+        <v>37.5</v>
       </c>
       <c r="AV15" t="n">
         <v>18.6</v>
@@ -20944,13 +20944,13 @@
         <v>14.1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>56.8</v>
       </c>
       <c r="BA15" t="n">
         <v>13.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.199999999999999</v>
+        <v>35.1</v>
       </c>
       <c r="BC15" t="n">
         <v>19.8</v>
@@ -20971,7 +20971,7 @@
         <v>17.3</v>
       </c>
       <c r="BI15" t="n">
-        <v>11.8</v>
+        <v>28.8</v>
       </c>
       <c r="BJ15" t="n">
         <v>17.5</v>
@@ -20980,13 +20980,13 @@
         <v>18.8</v>
       </c>
       <c r="BL15" t="n">
-        <v>9.9</v>
+        <v>29.2</v>
       </c>
       <c r="BM15" t="n">
         <v>15.2</v>
       </c>
       <c r="BN15" t="n">
-        <v>13.5</v>
+        <v>31.6</v>
       </c>
       <c r="BO15" t="n">
         <v>20.5</v>
@@ -20995,7 +20995,7 @@
         <v>14.2</v>
       </c>
       <c r="BQ15" t="n">
-        <v>12.4</v>
+        <v>49.8</v>
       </c>
       <c r="BR15" t="n">
         <v>16.8</v>
@@ -21007,13 +21007,13 @@
         <v>17.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.8</v>
+        <v>50.3</v>
       </c>
       <c r="BV15" t="n">
         <v>16.8</v>
       </c>
       <c r="BW15" t="n">
-        <v>12.7</v>
+        <v>44.1</v>
       </c>
       <c r="BX15" t="n">
         <v>17.7</v>
@@ -21022,7 +21022,7 @@
         <v>16.5</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>22.7</v>
       </c>
       <c r="CA15" t="n">
         <v>19.5</v>
@@ -21034,7 +21034,7 @@
         <v>26</v>
       </c>
       <c r="CD15" t="n">
-        <v>10.7</v>
+        <v>27.7</v>
       </c>
       <c r="CE15" t="n">
         <v>17.9</v>
@@ -21049,7 +21049,7 @@
         <v>14.2</v>
       </c>
       <c r="CI15" t="n">
-        <v>11.9</v>
+        <v>43.6</v>
       </c>
       <c r="CJ15" t="n">
         <v>19.8</v>
@@ -21067,7 +21067,7 @@
         <v>16.3</v>
       </c>
       <c r="CO15" t="n">
-        <v>12.9</v>
+        <v>49.7</v>
       </c>
       <c r="CP15" t="n">
         <v>14.7</v>
@@ -21076,13 +21076,13 @@
         <v>13.2</v>
       </c>
       <c r="CR15" t="n">
-        <v>16.9</v>
+        <v>40</v>
       </c>
       <c r="CS15" t="n">
         <v>24.5</v>
       </c>
       <c r="CT15" t="n">
-        <v>12.5</v>
+        <v>42.5</v>
       </c>
       <c r="CU15" t="n">
         <v>13.7</v>
@@ -21091,7 +21091,7 @@
         <v>11.3</v>
       </c>
       <c r="CW15" t="n">
-        <v>9.199999999999999</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="16">
@@ -22046,7 +22046,7 @@
         <v>24.6</v>
       </c>
       <c r="J19" t="n">
-        <v>13.8</v>
+        <v>57</v>
       </c>
       <c r="K19" t="n">
         <v>23.2</v>
@@ -22076,7 +22076,7 @@
         <v>19.1</v>
       </c>
       <c r="T19" t="n">
-        <v>16</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="U19" t="n">
         <v>23.2</v>
@@ -22085,7 +22085,7 @@
         <v>21</v>
       </c>
       <c r="W19" t="n">
-        <v>15.8</v>
+        <v>55.8</v>
       </c>
       <c r="X19" t="n">
         <v>28.7</v>
@@ -22097,7 +22097,7 @@
         <v>19</v>
       </c>
       <c r="AA19" t="n">
-        <v>16.6</v>
+        <v>54.3</v>
       </c>
       <c r="AB19" t="n">
         <v>20.7</v>
@@ -22118,7 +22118,7 @@
         <v>21.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>55.5</v>
       </c>
       <c r="AI19" t="n">
         <v>21.2</v>
@@ -22139,10 +22139,10 @@
         <v>19</v>
       </c>
       <c r="AO19" t="n">
-        <v>14.8</v>
+        <v>44.6</v>
       </c>
       <c r="AP19" t="n">
-        <v>16.3</v>
+        <v>60.2</v>
       </c>
       <c r="AQ19" t="n">
         <v>24.4</v>
@@ -22160,7 +22160,7 @@
         <v>19.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>15.1</v>
+        <v>48.7</v>
       </c>
       <c r="AW19" t="n">
         <v>18.8</v>
@@ -22172,16 +22172,16 @@
         <v>17.7</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>46.7</v>
       </c>
       <c r="BA19" t="n">
         <v>24.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>19.7</v>
+        <v>60</v>
       </c>
       <c r="BC19" t="n">
-        <v>17.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="BD19" t="n">
         <v>20.6</v>
@@ -22193,7 +22193,7 @@
         <v>17.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>12.5</v>
+        <v>46.8</v>
       </c>
       <c r="BH19" t="n">
         <v>23.5</v>
@@ -22202,7 +22202,7 @@
         <v>22.7</v>
       </c>
       <c r="BJ19" t="n">
-        <v>13</v>
+        <v>45.7</v>
       </c>
       <c r="BK19" t="n">
         <v>28.3</v>
@@ -22250,13 +22250,13 @@
         <v>29.3</v>
       </c>
       <c r="BZ19" t="n">
-        <v>15</v>
+        <v>68.7</v>
       </c>
       <c r="CA19" t="n">
         <v>21.9</v>
       </c>
       <c r="CB19" t="n">
-        <v>20.8</v>
+        <v>61.7</v>
       </c>
       <c r="CC19" t="n">
         <v>22.5</v>
@@ -22265,13 +22265,13 @@
         <v>22.4</v>
       </c>
       <c r="CE19" t="n">
-        <v>17.2</v>
+        <v>53.5</v>
       </c>
       <c r="CF19" t="n">
         <v>32.3</v>
       </c>
       <c r="CG19" t="n">
-        <v>14.2</v>
+        <v>54.9</v>
       </c>
       <c r="CH19" t="n">
         <v>20</v>
@@ -22289,7 +22289,7 @@
         <v>22</v>
       </c>
       <c r="CM19" t="n">
-        <v>17.4</v>
+        <v>45.7</v>
       </c>
       <c r="CN19" t="n">
         <v>23.6</v>
@@ -22301,7 +22301,7 @@
         <v>31.5</v>
       </c>
       <c r="CQ19" t="n">
-        <v>19.6</v>
+        <v>54</v>
       </c>
       <c r="CR19" t="n">
         <v>27.9</v>
@@ -24478,7 +24478,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.199999999999999</v>
+        <v>36.5</v>
       </c>
       <c r="C27" t="n">
         <v>20.1</v>
@@ -24514,7 +24514,7 @@
         <v>25</v>
       </c>
       <c r="N27" t="n">
-        <v>14.8</v>
+        <v>45.8</v>
       </c>
       <c r="O27" t="n">
         <v>20.9</v>
@@ -24553,7 +24553,7 @@
         <v>17.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>13.1</v>
+        <v>33.4</v>
       </c>
       <c r="AB27" t="n">
         <v>20.9</v>
@@ -25152,7 +25152,7 @@
         <v>22</v>
       </c>
       <c r="V29" t="n">
-        <v>14.2</v>
+        <v>39.4</v>
       </c>
       <c r="W29" t="n">
         <v>20.2</v>
@@ -25212,7 +25212,7 @@
         <v>16.8</v>
       </c>
       <c r="AP29" t="n">
-        <v>13.4</v>
+        <v>36.2</v>
       </c>
       <c r="AQ29" t="n">
         <v>19.3</v>
@@ -25314,7 +25314,7 @@
         <v>24.6</v>
       </c>
       <c r="BX29" t="n">
-        <v>15.7</v>
+        <v>49.1</v>
       </c>
       <c r="BY29" t="n">
         <v>21.9</v>
@@ -25411,7 +25411,7 @@
         <v>24.6</v>
       </c>
       <c r="F30" t="n">
-        <v>16.1</v>
+        <v>46.1</v>
       </c>
       <c r="G30" t="n">
         <v>12.3</v>
@@ -25423,22 +25423,22 @@
         <v>13.5</v>
       </c>
       <c r="J30" t="n">
-        <v>16.4</v>
+        <v>54.9</v>
       </c>
       <c r="K30" t="n">
         <v>25.5</v>
       </c>
       <c r="L30" t="n">
-        <v>11</v>
+        <v>51.2</v>
       </c>
       <c r="M30" t="n">
-        <v>16</v>
+        <v>38.9</v>
       </c>
       <c r="N30" t="n">
-        <v>12.9</v>
+        <v>36.5</v>
       </c>
       <c r="O30" t="n">
-        <v>12.3</v>
+        <v>42.4</v>
       </c>
       <c r="P30" t="n">
         <v>20.9</v>
@@ -25453,16 +25453,16 @@
         <v>21.9</v>
       </c>
       <c r="T30" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="U30" t="n">
         <v>19.6</v>
       </c>
       <c r="V30" t="n">
-        <v>14.3</v>
+        <v>48.9</v>
       </c>
       <c r="W30" t="n">
-        <v>17.1</v>
+        <v>58.7</v>
       </c>
       <c r="X30" t="n">
         <v>20.6</v>
@@ -25471,7 +25471,7 @@
         <v>19.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>17.2</v>
+        <v>51.2</v>
       </c>
       <c r="AA30" t="n">
         <v>19.3</v>
@@ -25489,7 +25489,7 @@
         <v>11.8</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>41.7</v>
       </c>
       <c r="AG30" t="n">
         <v>19.4</v>
@@ -25501,7 +25501,7 @@
         <v>16.4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14.8</v>
+        <v>52.7</v>
       </c>
       <c r="AK30" t="n">
         <v>20.1</v>
@@ -25510,7 +25510,7 @@
         <v>19.9</v>
       </c>
       <c r="AM30" t="n">
-        <v>13.7</v>
+        <v>63.1</v>
       </c>
       <c r="AN30" t="n">
         <v>25.3</v>
@@ -25543,7 +25543,7 @@
         <v>20</v>
       </c>
       <c r="AX30" t="n">
-        <v>13.2</v>
+        <v>43.8</v>
       </c>
       <c r="AY30" t="n">
         <v>23.5</v>
@@ -25552,13 +25552,13 @@
         <v>22.6</v>
       </c>
       <c r="BA30" t="n">
-        <v>14.8</v>
+        <v>41.4</v>
       </c>
       <c r="BB30" t="n">
         <v>26.1</v>
       </c>
       <c r="BC30" t="n">
-        <v>13.3</v>
+        <v>43.4</v>
       </c>
       <c r="BD30" t="n">
         <v>17.9</v>
@@ -25582,19 +25582,19 @@
         <v>19.3</v>
       </c>
       <c r="BK30" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="BL30" t="n">
         <v>18.8</v>
       </c>
       <c r="BM30" t="n">
-        <v>17.2</v>
+        <v>51.6</v>
       </c>
       <c r="BN30" t="n">
         <v>15.6</v>
       </c>
       <c r="BO30" t="n">
-        <v>18.5</v>
+        <v>58.8</v>
       </c>
       <c r="BP30" t="n">
         <v>14.2</v>
@@ -25603,7 +25603,7 @@
         <v>16.9</v>
       </c>
       <c r="BR30" t="n">
-        <v>14.4</v>
+        <v>50</v>
       </c>
       <c r="BS30" t="n">
         <v>18.3</v>
@@ -25642,7 +25642,7 @@
         <v>19</v>
       </c>
       <c r="CE30" t="n">
-        <v>17.1</v>
+        <v>65.2</v>
       </c>
       <c r="CF30" t="n">
         <v>18</v>
@@ -25651,7 +25651,7 @@
         <v>18</v>
       </c>
       <c r="CH30" t="n">
-        <v>14.4</v>
+        <v>39</v>
       </c>
       <c r="CI30" t="n">
         <v>17.1</v>
@@ -25666,7 +25666,7 @@
         <v>25.4</v>
       </c>
       <c r="CM30" t="n">
-        <v>15.5</v>
+        <v>48.8</v>
       </c>
       <c r="CN30" t="n">
         <v>16.7</v>
@@ -25678,10 +25678,10 @@
         <v>23.4</v>
       </c>
       <c r="CQ30" t="n">
-        <v>12.6</v>
+        <v>37.5</v>
       </c>
       <c r="CR30" t="n">
-        <v>11.2</v>
+        <v>54.5</v>
       </c>
       <c r="CS30" t="n">
         <v>17</v>
@@ -26028,7 +26028,7 @@
         <v>15.3</v>
       </c>
       <c r="G32" t="n">
-        <v>12.4</v>
+        <v>32.7</v>
       </c>
       <c r="H32" t="n">
         <v>18.6</v>
@@ -26040,7 +26040,7 @@
         <v>19.4</v>
       </c>
       <c r="K32" t="n">
-        <v>13.2</v>
+        <v>37.8</v>
       </c>
       <c r="L32" t="n">
         <v>23.7</v>
@@ -26061,10 +26061,10 @@
         <v>23.4</v>
       </c>
       <c r="R32" t="n">
-        <v>11.9</v>
+        <v>35.7</v>
       </c>
       <c r="S32" t="n">
-        <v>15.2</v>
+        <v>43.2</v>
       </c>
       <c r="T32" t="n">
         <v>22.3</v>
@@ -26112,7 +26112,7 @@
         <v>20.4</v>
       </c>
       <c r="AI32" t="n">
-        <v>12.7</v>
+        <v>43.6</v>
       </c>
       <c r="AJ32" t="n">
         <v>13.8</v>
@@ -26139,13 +26139,13 @@
         <v>14.9</v>
       </c>
       <c r="AR32" t="n">
-        <v>16.7</v>
+        <v>44</v>
       </c>
       <c r="AS32" t="n">
-        <v>17.2</v>
+        <v>60.7</v>
       </c>
       <c r="AT32" t="n">
-        <v>14.2</v>
+        <v>46.9</v>
       </c>
       <c r="AU32" t="n">
         <v>18.7</v>
@@ -26172,10 +26172,10 @@
         <v>17.9</v>
       </c>
       <c r="BC32" t="n">
-        <v>16.8</v>
+        <v>58.7</v>
       </c>
       <c r="BD32" t="n">
-        <v>10.2</v>
+        <v>40.8</v>
       </c>
       <c r="BE32" t="n">
         <v>16</v>
@@ -26193,7 +26193,7 @@
         <v>26.8</v>
       </c>
       <c r="BJ32" t="n">
-        <v>16.5</v>
+        <v>38.5</v>
       </c>
       <c r="BK32" t="n">
         <v>18.2</v>
@@ -26211,7 +26211,7 @@
         <v>21.8</v>
       </c>
       <c r="BP32" t="n">
-        <v>8.800000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="BQ32" t="n">
         <v>14.4</v>
@@ -26220,7 +26220,7 @@
         <v>20.9</v>
       </c>
       <c r="BS32" t="n">
-        <v>12.4</v>
+        <v>56.5</v>
       </c>
       <c r="BT32" t="n">
         <v>19.7</v>
@@ -26232,7 +26232,7 @@
         <v>25.3</v>
       </c>
       <c r="BW32" t="n">
-        <v>14</v>
+        <v>53.6</v>
       </c>
       <c r="BX32" t="n">
         <v>19.4</v>
@@ -26247,7 +26247,7 @@
         <v>19.8</v>
       </c>
       <c r="CB32" t="n">
-        <v>13.5</v>
+        <v>51</v>
       </c>
       <c r="CC32" t="n">
         <v>22</v>
@@ -26256,7 +26256,7 @@
         <v>21.1</v>
       </c>
       <c r="CE32" t="n">
-        <v>12.3</v>
+        <v>43.7</v>
       </c>
       <c r="CF32" t="n">
         <v>19.7</v>
@@ -26286,7 +26286,7 @@
         <v>20.2</v>
       </c>
       <c r="CO32" t="n">
-        <v>13.4</v>
+        <v>50.1</v>
       </c>
       <c r="CP32" t="n">
         <v>17.2</v>
@@ -26295,7 +26295,7 @@
         <v>18.3</v>
       </c>
       <c r="CR32" t="n">
-        <v>17</v>
+        <v>47.7</v>
       </c>
       <c r="CS32" t="n">
         <v>21.1</v>
@@ -26687,7 +26687,7 @@
         <v>26.6</v>
       </c>
       <c r="V34" t="n">
-        <v>10.3</v>
+        <v>25.5</v>
       </c>
       <c r="W34" t="n">
         <v>26.1</v>
@@ -26795,7 +26795,7 @@
         <v>24.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>8.6</v>
+        <v>28.8</v>
       </c>
       <c r="BG34" t="n">
         <v>12.3</v>
@@ -26870,7 +26870,7 @@
         <v>19.4</v>
       </c>
       <c r="CE34" t="n">
-        <v>7.6</v>
+        <v>24.2</v>
       </c>
       <c r="CF34" t="n">
         <v>20.6</v>
@@ -26949,7 +26949,7 @@
         <v>13.2</v>
       </c>
       <c r="G35" t="n">
-        <v>7.4</v>
+        <v>30.1</v>
       </c>
       <c r="H35" t="n">
         <v>12.6</v>
@@ -26970,7 +26970,7 @@
         <v>13.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6.6</v>
+        <v>36.2</v>
       </c>
       <c r="O35" t="n">
         <v>22.4</v>
@@ -27120,7 +27120,7 @@
         <v>14.1</v>
       </c>
       <c r="BL35" t="n">
-        <v>4.2</v>
+        <v>12.8</v>
       </c>
       <c r="BM35" t="n">
         <v>22.8</v>
@@ -27165,7 +27165,7 @@
         <v>11.2</v>
       </c>
       <c r="CA35" t="n">
-        <v>8.1</v>
+        <v>31.4</v>
       </c>
       <c r="CB35" t="n">
         <v>26.3</v>
@@ -27548,13 +27548,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.4</v>
+        <v>47.4</v>
       </c>
       <c r="C37" t="n">
-        <v>11.3</v>
+        <v>48</v>
       </c>
       <c r="D37" t="n">
-        <v>12.3</v>
+        <v>53.6</v>
       </c>
       <c r="E37" t="n">
         <v>18.6</v>
@@ -27563,7 +27563,7 @@
         <v>16.8</v>
       </c>
       <c r="G37" t="n">
-        <v>14</v>
+        <v>52.9</v>
       </c>
       <c r="H37" t="n">
         <v>18.1</v>
@@ -27572,19 +27572,19 @@
         <v>16.6</v>
       </c>
       <c r="J37" t="n">
-        <v>11</v>
+        <v>55.4</v>
       </c>
       <c r="K37" t="n">
-        <v>11.2</v>
+        <v>47.4</v>
       </c>
       <c r="L37" t="n">
         <v>17.1</v>
       </c>
       <c r="M37" t="n">
-        <v>11.8</v>
+        <v>29.6</v>
       </c>
       <c r="N37" t="n">
-        <v>16.5</v>
+        <v>44.7</v>
       </c>
       <c r="O37" t="n">
         <v>21.8</v>
@@ -27593,31 +27593,31 @@
         <v>22.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>11.6</v>
+        <v>54.6</v>
       </c>
       <c r="R37" t="n">
-        <v>14.5</v>
+        <v>53.6</v>
       </c>
       <c r="S37" t="n">
-        <v>11.9</v>
+        <v>45.1</v>
       </c>
       <c r="T37" t="n">
         <v>18.2</v>
       </c>
       <c r="U37" t="n">
-        <v>13.2</v>
+        <v>45.7</v>
       </c>
       <c r="V37" t="n">
-        <v>11.6</v>
+        <v>34.4</v>
       </c>
       <c r="W37" t="n">
-        <v>13</v>
+        <v>44.2</v>
       </c>
       <c r="X37" t="n">
         <v>19.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>11.5</v>
+        <v>35.8</v>
       </c>
       <c r="Z37" t="n">
         <v>19.3</v>
@@ -27629,25 +27629,25 @@
         <v>17.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.5</v>
+        <v>47.1</v>
       </c>
       <c r="AD37" t="n">
         <v>15.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>9.9</v>
+        <v>34.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>11.6</v>
+        <v>61.2</v>
       </c>
       <c r="AG37" t="n">
         <v>20.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>9.9</v>
+        <v>37.1</v>
       </c>
       <c r="AI37" t="n">
-        <v>15.4</v>
+        <v>37.5</v>
       </c>
       <c r="AJ37" t="n">
         <v>17.3</v>
@@ -27665,22 +27665,22 @@
         <v>25.9</v>
       </c>
       <c r="AO37" t="n">
-        <v>12.1</v>
+        <v>37.4</v>
       </c>
       <c r="AP37" t="n">
-        <v>10.2</v>
+        <v>48.3</v>
       </c>
       <c r="AQ37" t="n">
-        <v>9.6</v>
+        <v>42.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>13.7</v>
+        <v>41.9</v>
       </c>
       <c r="AS37" t="n">
-        <v>12.5</v>
+        <v>51.8</v>
       </c>
       <c r="AT37" t="n">
-        <v>14.8</v>
+        <v>43.4</v>
       </c>
       <c r="AU37" t="n">
         <v>19</v>
@@ -27689,7 +27689,7 @@
         <v>19.7</v>
       </c>
       <c r="AW37" t="n">
-        <v>11.6</v>
+        <v>43.4</v>
       </c>
       <c r="AX37" t="n">
         <v>19.2</v>
@@ -27698,10 +27698,10 @@
         <v>22.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>13.1</v>
+        <v>42.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>10.8</v>
+        <v>43.9</v>
       </c>
       <c r="BB37" t="n">
         <v>14.1</v>
@@ -27710,10 +27710,10 @@
         <v>15.9</v>
       </c>
       <c r="BD37" t="n">
-        <v>15.6</v>
+        <v>48.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>14.6</v>
+        <v>44.2</v>
       </c>
       <c r="BF37" t="n">
         <v>20.1</v>
@@ -27734,7 +27734,7 @@
         <v>20.7</v>
       </c>
       <c r="BL37" t="n">
-        <v>14.1</v>
+        <v>57.4</v>
       </c>
       <c r="BM37" t="n">
         <v>22.1</v>
@@ -27749,40 +27749,40 @@
         <v>13.2</v>
       </c>
       <c r="BQ37" t="n">
-        <v>13.3</v>
+        <v>32.6</v>
       </c>
       <c r="BR37" t="n">
         <v>21.8</v>
       </c>
       <c r="BS37" t="n">
-        <v>13</v>
+        <v>43.1</v>
       </c>
       <c r="BT37" t="n">
         <v>19.1</v>
       </c>
       <c r="BU37" t="n">
-        <v>12.7</v>
+        <v>37.3</v>
       </c>
       <c r="BV37" t="n">
         <v>18.1</v>
       </c>
       <c r="BW37" t="n">
-        <v>15.4</v>
+        <v>46.7</v>
       </c>
       <c r="BX37" t="n">
-        <v>16.2</v>
+        <v>56.9</v>
       </c>
       <c r="BY37" t="n">
-        <v>11.2</v>
+        <v>37.2</v>
       </c>
       <c r="BZ37" t="n">
         <v>22.3</v>
       </c>
       <c r="CA37" t="n">
-        <v>17.8</v>
+        <v>49.8</v>
       </c>
       <c r="CB37" t="n">
-        <v>9.199999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="CC37" t="n">
         <v>22.5</v>
@@ -27794,22 +27794,22 @@
         <v>24.6</v>
       </c>
       <c r="CF37" t="n">
-        <v>7.3</v>
+        <v>43.2</v>
       </c>
       <c r="CG37" t="n">
-        <v>11.6</v>
+        <v>35.7</v>
       </c>
       <c r="CH37" t="n">
-        <v>14.2</v>
+        <v>61</v>
       </c>
       <c r="CI37" t="n">
-        <v>8.6</v>
+        <v>43.7</v>
       </c>
       <c r="CJ37" t="n">
         <v>22.9</v>
       </c>
       <c r="CK37" t="n">
-        <v>14.3</v>
+        <v>42.7</v>
       </c>
       <c r="CL37" t="n">
         <v>13.1</v>
@@ -27821,10 +27821,10 @@
         <v>20.5</v>
       </c>
       <c r="CO37" t="n">
-        <v>14.7</v>
+        <v>38</v>
       </c>
       <c r="CP37" t="n">
-        <v>11.3</v>
+        <v>33.3</v>
       </c>
       <c r="CQ37" t="n">
         <v>16.5</v>
@@ -27833,7 +27833,7 @@
         <v>21.7</v>
       </c>
       <c r="CS37" t="n">
-        <v>6.6</v>
+        <v>51.2</v>
       </c>
       <c r="CT37" t="n">
         <v>19</v>
@@ -27842,10 +27842,10 @@
         <v>21.6</v>
       </c>
       <c r="CV37" t="n">
-        <v>16.2</v>
+        <v>57.6</v>
       </c>
       <c r="CW37" t="n">
-        <v>12.9</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="38">
@@ -27906,7 +27906,7 @@
         <v>17.2</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>20.9</v>
       </c>
       <c r="T38" t="n">
         <v>9.800000000000001</v>
@@ -28062,7 +28062,7 @@
         <v>23.8</v>
       </c>
       <c r="BS38" t="n">
-        <v>6.3</v>
+        <v>14.9</v>
       </c>
       <c r="BT38" t="n">
         <v>16.8</v>
@@ -28104,7 +28104,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CG38" t="n">
-        <v>5.6</v>
+        <v>32.7</v>
       </c>
       <c r="CH38" t="n">
         <v>15.9</v>
@@ -28162,304 +28162,304 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12.4</v>
+        <v>51.1</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D39" t="n">
-        <v>9.1</v>
+        <v>62.5</v>
       </c>
       <c r="E39" t="n">
-        <v>7.9</v>
+        <v>41.8</v>
       </c>
       <c r="F39" t="n">
-        <v>4.4</v>
+        <v>43.4</v>
       </c>
       <c r="G39" t="n">
-        <v>6.8</v>
+        <v>56.3</v>
       </c>
       <c r="H39" t="n">
-        <v>2.1</v>
+        <v>44.7</v>
       </c>
       <c r="I39" t="n">
         <v>16.3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="K39" t="n">
-        <v>7.6</v>
+        <v>60.8</v>
       </c>
       <c r="L39" t="n">
-        <v>5.2</v>
+        <v>42.9</v>
       </c>
       <c r="M39" t="n">
-        <v>10.9</v>
+        <v>41.1</v>
       </c>
       <c r="N39" t="n">
         <v>15.3</v>
       </c>
       <c r="O39" t="n">
-        <v>12</v>
+        <v>47.1</v>
       </c>
       <c r="P39" t="n">
-        <v>8.6</v>
+        <v>48.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>11.7</v>
+        <v>46.7</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>54.3</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>41.1</v>
       </c>
       <c r="T39" t="n">
-        <v>7.7</v>
+        <v>41.8</v>
       </c>
       <c r="U39" t="n">
-        <v>6.1</v>
+        <v>55.2</v>
       </c>
       <c r="V39" t="n">
-        <v>13.1</v>
+        <v>47.3</v>
       </c>
       <c r="W39" t="n">
-        <v>5.4</v>
+        <v>39.8</v>
       </c>
       <c r="X39" t="n">
-        <v>7.4</v>
+        <v>54.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>7.5</v>
+        <v>53.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>6.6</v>
+        <v>40.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>6.4</v>
+        <v>48.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>8.4</v>
+        <v>47.8</v>
       </c>
       <c r="AC39" t="n">
-        <v>10.6</v>
+        <v>34.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>11.3</v>
+        <v>53.4</v>
       </c>
       <c r="AE39" t="n">
-        <v>5.5</v>
+        <v>51.2</v>
       </c>
       <c r="AF39" t="n">
         <v>15.6</v>
       </c>
       <c r="AG39" t="n">
-        <v>10.7</v>
+        <v>39.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.1</v>
+        <v>43.1</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.8</v>
+        <v>46.5</v>
       </c>
       <c r="AJ39" t="n">
-        <v>7.8</v>
+        <v>43.3</v>
       </c>
       <c r="AK39" t="n">
-        <v>8.699999999999999</v>
+        <v>43.9</v>
       </c>
       <c r="AL39" t="n">
-        <v>11.8</v>
+        <v>36</v>
       </c>
       <c r="AM39" t="n">
         <v>17.3</v>
       </c>
       <c r="AN39" t="n">
-        <v>3.4</v>
+        <v>40.2</v>
       </c>
       <c r="AO39" t="n">
-        <v>10.5</v>
+        <v>47.3</v>
       </c>
       <c r="AP39" t="n">
-        <v>6.1</v>
+        <v>42.2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>12.1</v>
+        <v>42.9</v>
       </c>
       <c r="AR39" t="n">
-        <v>15.4</v>
+        <v>49.4</v>
       </c>
       <c r="AS39" t="n">
-        <v>12.1</v>
+        <v>39.2</v>
       </c>
       <c r="AT39" t="n">
-        <v>5.6</v>
+        <v>41.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.5</v>
+        <v>49.9</v>
       </c>
       <c r="AV39" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="AW39" t="n">
-        <v>5.1</v>
+        <v>54.7</v>
       </c>
       <c r="AX39" t="n">
-        <v>8.6</v>
+        <v>50.7</v>
       </c>
       <c r="AY39" t="n">
-        <v>5.6</v>
+        <v>50.2</v>
       </c>
       <c r="AZ39" t="n">
-        <v>6.4</v>
+        <v>31</v>
       </c>
       <c r="BA39" t="n">
-        <v>9.199999999999999</v>
+        <v>41.7</v>
       </c>
       <c r="BB39" t="n">
-        <v>8.6</v>
+        <v>41.3</v>
       </c>
       <c r="BC39" t="n">
-        <v>9.6</v>
+        <v>49.9</v>
       </c>
       <c r="BD39" t="n">
-        <v>13.2</v>
+        <v>56.7</v>
       </c>
       <c r="BE39" t="n">
-        <v>17.8</v>
+        <v>56.9</v>
       </c>
       <c r="BF39" t="n">
-        <v>13.4</v>
+        <v>48.9</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.4</v>
+        <v>33.6</v>
       </c>
       <c r="BH39" t="n">
-        <v>10.5</v>
+        <v>49.8</v>
       </c>
       <c r="BI39" t="n">
-        <v>6.7</v>
+        <v>47.8</v>
       </c>
       <c r="BJ39" t="n">
-        <v>16.5</v>
+        <v>61</v>
       </c>
       <c r="BK39" t="n">
-        <v>10.1</v>
+        <v>53.2</v>
       </c>
       <c r="BL39" t="n">
-        <v>4.5</v>
+        <v>46.9</v>
       </c>
       <c r="BM39" t="n">
-        <v>13.5</v>
+        <v>33.7</v>
       </c>
       <c r="BN39" t="n">
-        <v>7.8</v>
+        <v>48.7</v>
       </c>
       <c r="BO39" t="n">
-        <v>2.6</v>
+        <v>43.1</v>
       </c>
       <c r="BP39" t="n">
-        <v>10.9</v>
+        <v>58.1</v>
       </c>
       <c r="BQ39" t="n">
-        <v>11.1</v>
+        <v>54.3</v>
       </c>
       <c r="BR39" t="n">
         <v>12.5</v>
       </c>
       <c r="BS39" t="n">
-        <v>6</v>
+        <v>60.3</v>
       </c>
       <c r="BT39" t="n">
-        <v>6.1</v>
+        <v>59.2</v>
       </c>
       <c r="BU39" t="n">
-        <v>12.3</v>
+        <v>43.1</v>
       </c>
       <c r="BV39" t="n">
-        <v>3.5</v>
+        <v>64.5</v>
       </c>
       <c r="BW39" t="n">
-        <v>5.6</v>
+        <v>43.9</v>
       </c>
       <c r="BX39" t="n">
-        <v>7.6</v>
+        <v>58.4</v>
       </c>
       <c r="BY39" t="n">
-        <v>8.1</v>
+        <v>46.9</v>
       </c>
       <c r="BZ39" t="n">
         <v>14.4</v>
       </c>
       <c r="CA39" t="n">
-        <v>12.5</v>
+        <v>45.7</v>
       </c>
       <c r="CB39" t="n">
-        <v>6.4</v>
+        <v>44.8</v>
       </c>
       <c r="CC39" t="n">
-        <v>12.8</v>
+        <v>47.7</v>
       </c>
       <c r="CD39" t="n">
         <v>17.8</v>
       </c>
       <c r="CE39" t="n">
-        <v>7</v>
+        <v>36.1</v>
       </c>
       <c r="CF39" t="n">
-        <v>9.9</v>
+        <v>44.9</v>
       </c>
       <c r="CG39" t="n">
-        <v>7.3</v>
+        <v>36.6</v>
       </c>
       <c r="CH39" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="CI39" t="n">
-        <v>6.3</v>
+        <v>41.9</v>
       </c>
       <c r="CJ39" t="n">
-        <v>11.2</v>
+        <v>36.3</v>
       </c>
       <c r="CK39" t="n">
-        <v>11.8</v>
+        <v>55.8</v>
       </c>
       <c r="CL39" t="n">
-        <v>6.1</v>
+        <v>53.1</v>
       </c>
       <c r="CM39" t="n">
-        <v>4.9</v>
+        <v>39.1</v>
       </c>
       <c r="CN39" t="n">
-        <v>6.2</v>
+        <v>44.1</v>
       </c>
       <c r="CO39" t="n">
         <v>15.5</v>
       </c>
       <c r="CP39" t="n">
-        <v>5.5</v>
+        <v>43.5</v>
       </c>
       <c r="CQ39" t="n">
-        <v>10.2</v>
+        <v>60.1</v>
       </c>
       <c r="CR39" t="n">
-        <v>6.1</v>
+        <v>44.2</v>
       </c>
       <c r="CS39" t="n">
-        <v>6.9</v>
+        <v>59.3</v>
       </c>
       <c r="CT39" t="n">
-        <v>15.9</v>
+        <v>42.1</v>
       </c>
       <c r="CU39" t="n">
-        <v>12.1</v>
+        <v>56.9</v>
       </c>
       <c r="CV39" t="n">
-        <v>8.699999999999999</v>
+        <v>33.8</v>
       </c>
       <c r="CW39" t="n">
-        <v>5.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40">
@@ -28532,7 +28532,7 @@
         <v>27.6</v>
       </c>
       <c r="W40" t="n">
-        <v>10</v>
+        <v>26.6</v>
       </c>
       <c r="X40" t="n">
         <v>22.4</v>
@@ -28703,7 +28703,7 @@
         <v>14.2</v>
       </c>
       <c r="CB40" t="n">
-        <v>4.9</v>
+        <v>12.4</v>
       </c>
       <c r="CC40" t="n">
         <v>19.7</v>
@@ -28766,7 +28766,7 @@
         <v>15.2</v>
       </c>
       <c r="CW40" t="n">
-        <v>9.4</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="41">
@@ -28782,7 +28782,7 @@
         <v>21</v>
       </c>
       <c r="D41" t="n">
-        <v>12.7</v>
+        <v>42.8</v>
       </c>
       <c r="E41" t="n">
         <v>18.2</v>
@@ -28797,7 +28797,7 @@
         <v>15.9</v>
       </c>
       <c r="I41" t="n">
-        <v>9.800000000000001</v>
+        <v>28.5</v>
       </c>
       <c r="J41" t="n">
         <v>11.8</v>
@@ -28812,13 +28812,13 @@
         <v>14.4</v>
       </c>
       <c r="N41" t="n">
-        <v>11.4</v>
+        <v>38.4</v>
       </c>
       <c r="O41" t="n">
-        <v>12.3</v>
+        <v>38.7</v>
       </c>
       <c r="P41" t="n">
-        <v>14.6</v>
+        <v>42</v>
       </c>
       <c r="Q41" t="n">
         <v>12.1</v>
@@ -28872,7 +28872,7 @@
         <v>28.6</v>
       </c>
       <c r="AH41" t="n">
-        <v>10.7</v>
+        <v>43</v>
       </c>
       <c r="AI41" t="n">
         <v>16.1</v>
@@ -28887,7 +28887,7 @@
         <v>19.3</v>
       </c>
       <c r="AM41" t="n">
-        <v>8.800000000000001</v>
+        <v>35.3</v>
       </c>
       <c r="AN41" t="n">
         <v>16.2</v>
@@ -28902,7 +28902,7 @@
         <v>11.9</v>
       </c>
       <c r="AR41" t="n">
-        <v>10.7</v>
+        <v>45.2</v>
       </c>
       <c r="AS41" t="n">
         <v>10.5</v>
@@ -28911,7 +28911,7 @@
         <v>15.2</v>
       </c>
       <c r="AU41" t="n">
-        <v>13.6</v>
+        <v>33.5</v>
       </c>
       <c r="AV41" t="n">
         <v>17.4</v>
@@ -28938,7 +28938,7 @@
         <v>19.4</v>
       </c>
       <c r="BD41" t="n">
-        <v>10.3</v>
+        <v>40</v>
       </c>
       <c r="BE41" t="n">
         <v>15.6</v>
@@ -28959,7 +28959,7 @@
         <v>18.2</v>
       </c>
       <c r="BK41" t="n">
-        <v>8.699999999999999</v>
+        <v>37.3</v>
       </c>
       <c r="BL41" t="n">
         <v>13.1</v>
@@ -28980,13 +28980,13 @@
         <v>23.3</v>
       </c>
       <c r="BR41" t="n">
-        <v>10.2</v>
+        <v>41.9</v>
       </c>
       <c r="BS41" t="n">
         <v>14.4</v>
       </c>
       <c r="BT41" t="n">
-        <v>6.8</v>
+        <v>29.6</v>
       </c>
       <c r="BU41" t="n">
         <v>15.2</v>
@@ -28998,16 +28998,16 @@
         <v>19.9</v>
       </c>
       <c r="BX41" t="n">
-        <v>9.5</v>
+        <v>40.2</v>
       </c>
       <c r="BY41" t="n">
         <v>17.4</v>
       </c>
       <c r="BZ41" t="n">
-        <v>6.5</v>
+        <v>28.3</v>
       </c>
       <c r="CA41" t="n">
-        <v>8.800000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="CB41" t="n">
         <v>10.3</v>
@@ -29022,7 +29022,7 @@
         <v>16.9</v>
       </c>
       <c r="CF41" t="n">
-        <v>11</v>
+        <v>42.8</v>
       </c>
       <c r="CG41" t="n">
         <v>18.2</v>
@@ -29040,10 +29040,10 @@
         <v>24.1</v>
       </c>
       <c r="CL41" t="n">
-        <v>9.5</v>
+        <v>36.9</v>
       </c>
       <c r="CM41" t="n">
-        <v>14.4</v>
+        <v>39.3</v>
       </c>
       <c r="CN41" t="n">
         <v>18.3</v>
@@ -29067,7 +29067,7 @@
         <v>11.1</v>
       </c>
       <c r="CU41" t="n">
-        <v>9.300000000000001</v>
+        <v>36</v>
       </c>
       <c r="CV41" t="n">
         <v>14.5</v>
@@ -29426,7 +29426,7 @@
         <v>20.1</v>
       </c>
       <c r="N43" t="n">
-        <v>15.7</v>
+        <v>53.4</v>
       </c>
       <c r="O43" t="n">
         <v>18.3</v>
@@ -29453,7 +29453,7 @@
         <v>18.5</v>
       </c>
       <c r="W43" t="n">
-        <v>12.4</v>
+        <v>38.3</v>
       </c>
       <c r="X43" t="n">
         <v>11.2</v>
@@ -29567,7 +29567,7 @@
         <v>16.2</v>
       </c>
       <c r="BI43" t="n">
-        <v>9.5</v>
+        <v>32.2</v>
       </c>
       <c r="BJ43" t="n">
         <v>17.7</v>
@@ -29654,7 +29654,7 @@
         <v>24.8</v>
       </c>
       <c r="CL43" t="n">
-        <v>12.7</v>
+        <v>35.4</v>
       </c>
       <c r="CM43" t="n">
         <v>17.4</v>
@@ -29700,10 +29700,10 @@
         <v>17.8</v>
       </c>
       <c r="C44" t="n">
-        <v>6.1</v>
+        <v>46.5</v>
       </c>
       <c r="D44" t="n">
-        <v>13.1</v>
+        <v>39.4</v>
       </c>
       <c r="E44" t="n">
         <v>17.7</v>
@@ -29712,25 +29712,25 @@
         <v>18.7</v>
       </c>
       <c r="G44" t="n">
-        <v>15.9</v>
+        <v>42</v>
       </c>
       <c r="H44" t="n">
         <v>19.1</v>
       </c>
       <c r="I44" t="n">
-        <v>8.1</v>
+        <v>42.2</v>
       </c>
       <c r="J44" t="n">
-        <v>13.8</v>
+        <v>60.8</v>
       </c>
       <c r="K44" t="n">
-        <v>14.5</v>
+        <v>47.3</v>
       </c>
       <c r="L44" t="n">
-        <v>4.2</v>
+        <v>49.3</v>
       </c>
       <c r="M44" t="n">
-        <v>12.5</v>
+        <v>46.3</v>
       </c>
       <c r="N44" t="n">
         <v>20.4</v>
@@ -29739,25 +29739,25 @@
         <v>16.1</v>
       </c>
       <c r="P44" t="n">
-        <v>16.6</v>
+        <v>45.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.8</v>
+        <v>49.2</v>
       </c>
       <c r="R44" t="n">
-        <v>10.8</v>
+        <v>37.3</v>
       </c>
       <c r="S44" t="n">
-        <v>16.7</v>
+        <v>42.7</v>
       </c>
       <c r="T44" t="n">
-        <v>9.300000000000001</v>
+        <v>41.3</v>
       </c>
       <c r="U44" t="n">
-        <v>5.2</v>
+        <v>53.6</v>
       </c>
       <c r="V44" t="n">
-        <v>11.4</v>
+        <v>57.1</v>
       </c>
       <c r="W44" t="n">
         <v>19.3</v>
@@ -29766,25 +29766,25 @@
         <v>16.9</v>
       </c>
       <c r="Y44" t="n">
-        <v>16.2</v>
+        <v>51.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.4</v>
+        <v>47.3</v>
       </c>
       <c r="AA44" t="n">
-        <v>14.4</v>
+        <v>39.3</v>
       </c>
       <c r="AB44" t="n">
-        <v>15.7</v>
+        <v>47.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="AD44" t="n">
         <v>17.6</v>
       </c>
       <c r="AE44" t="n">
-        <v>9.4</v>
+        <v>56.2</v>
       </c>
       <c r="AF44" t="n">
         <v>18.4</v>
@@ -29793,82 +29793,82 @@
         <v>15.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>8.699999999999999</v>
+        <v>37.6</v>
       </c>
       <c r="AI44" t="n">
         <v>19.6</v>
       </c>
       <c r="AJ44" t="n">
-        <v>14.9</v>
+        <v>34.7</v>
       </c>
       <c r="AK44" t="n">
-        <v>6.4</v>
+        <v>48.1</v>
       </c>
       <c r="AL44" t="n">
-        <v>12.5</v>
+        <v>41.9</v>
       </c>
       <c r="AM44" t="n">
-        <v>6.8</v>
+        <v>44.7</v>
       </c>
       <c r="AN44" t="n">
-        <v>9.4</v>
+        <v>57.1</v>
       </c>
       <c r="AO44" t="n">
-        <v>9.199999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="AP44" t="n">
-        <v>5.9</v>
+        <v>46.7</v>
       </c>
       <c r="AQ44" t="n">
-        <v>5.7</v>
+        <v>38.7</v>
       </c>
       <c r="AR44" t="n">
-        <v>10.9</v>
+        <v>31.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>11.2</v>
+        <v>38</v>
       </c>
       <c r="AT44" t="n">
-        <v>18.2</v>
+        <v>46.9</v>
       </c>
       <c r="AU44" t="n">
         <v>18.1</v>
       </c>
       <c r="AV44" t="n">
-        <v>7.8</v>
+        <v>43.3</v>
       </c>
       <c r="AW44" t="n">
-        <v>9.9</v>
+        <v>57.2</v>
       </c>
       <c r="AX44" t="n">
         <v>19.7</v>
       </c>
       <c r="AY44" t="n">
-        <v>13.1</v>
+        <v>45.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>12</v>
+        <v>42.8</v>
       </c>
       <c r="BA44" t="n">
-        <v>9.699999999999999</v>
+        <v>47.6</v>
       </c>
       <c r="BB44" t="n">
-        <v>11.1</v>
+        <v>44.6</v>
       </c>
       <c r="BC44" t="n">
         <v>18.9</v>
       </c>
       <c r="BD44" t="n">
-        <v>13.5</v>
+        <v>49.9</v>
       </c>
       <c r="BE44" t="n">
-        <v>13.7</v>
+        <v>48.4</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.6</v>
+        <v>38.6</v>
       </c>
       <c r="BG44" t="n">
-        <v>14.7</v>
+        <v>50.6</v>
       </c>
       <c r="BH44" t="n">
         <v>16.2</v>
@@ -29877,121 +29877,121 @@
         <v>20.3</v>
       </c>
       <c r="BJ44" t="n">
-        <v>14.7</v>
+        <v>38.9</v>
       </c>
       <c r="BK44" t="n">
-        <v>9.199999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="BL44" t="n">
-        <v>11</v>
+        <v>44.9</v>
       </c>
       <c r="BM44" t="n">
-        <v>16.3</v>
+        <v>38.1</v>
       </c>
       <c r="BN44" t="n">
-        <v>13.1</v>
+        <v>37.3</v>
       </c>
       <c r="BO44" t="n">
-        <v>10.1</v>
+        <v>40</v>
       </c>
       <c r="BP44" t="n">
         <v>16.2</v>
       </c>
       <c r="BQ44" t="n">
-        <v>16.2</v>
+        <v>57.7</v>
       </c>
       <c r="BR44" t="n">
-        <v>15.3</v>
+        <v>57.4</v>
       </c>
       <c r="BS44" t="n">
-        <v>12.6</v>
+        <v>35.5</v>
       </c>
       <c r="BT44" t="n">
-        <v>12.7</v>
+        <v>40</v>
       </c>
       <c r="BU44" t="n">
-        <v>8.4</v>
+        <v>48.2</v>
       </c>
       <c r="BV44" t="n">
-        <v>14.1</v>
+        <v>43.4</v>
       </c>
       <c r="BW44" t="n">
-        <v>12.1</v>
+        <v>51.3</v>
       </c>
       <c r="BX44" t="n">
-        <v>13.7</v>
+        <v>51.9</v>
       </c>
       <c r="BY44" t="n">
-        <v>6.9</v>
+        <v>60.3</v>
       </c>
       <c r="BZ44" t="n">
-        <v>10</v>
+        <v>42.9</v>
       </c>
       <c r="CA44" t="n">
-        <v>14</v>
+        <v>55.3</v>
       </c>
       <c r="CB44" t="n">
         <v>18.1</v>
       </c>
       <c r="CC44" t="n">
-        <v>12.7</v>
+        <v>54.6</v>
       </c>
       <c r="CD44" t="n">
-        <v>14.1</v>
+        <v>52</v>
       </c>
       <c r="CE44" t="n">
-        <v>12.6</v>
+        <v>47.9</v>
       </c>
       <c r="CF44" t="n">
-        <v>13.3</v>
+        <v>48.3</v>
       </c>
       <c r="CG44" t="n">
-        <v>8.699999999999999</v>
+        <v>48.1</v>
       </c>
       <c r="CH44" t="n">
         <v>15</v>
       </c>
       <c r="CI44" t="n">
-        <v>12.4</v>
+        <v>43.2</v>
       </c>
       <c r="CJ44" t="n">
-        <v>10.3</v>
+        <v>55.7</v>
       </c>
       <c r="CK44" t="n">
-        <v>7.3</v>
+        <v>46.1</v>
       </c>
       <c r="CL44" t="n">
-        <v>14.5</v>
+        <v>49.2</v>
       </c>
       <c r="CM44" t="n">
-        <v>12.4</v>
+        <v>36.9</v>
       </c>
       <c r="CN44" t="n">
-        <v>9</v>
+        <v>39.7</v>
       </c>
       <c r="CO44" t="n">
         <v>19</v>
       </c>
       <c r="CP44" t="n">
-        <v>10</v>
+        <v>37.8</v>
       </c>
       <c r="CQ44" t="n">
-        <v>6.3</v>
+        <v>52.3</v>
       </c>
       <c r="CR44" t="n">
-        <v>9</v>
+        <v>49.4</v>
       </c>
       <c r="CS44" t="n">
-        <v>13.1</v>
+        <v>63.5</v>
       </c>
       <c r="CT44" t="n">
-        <v>11.3</v>
+        <v>41.2</v>
       </c>
       <c r="CU44" t="n">
-        <v>10.8</v>
+        <v>32.3</v>
       </c>
       <c r="CV44" t="n">
-        <v>9.800000000000001</v>
+        <v>34.5</v>
       </c>
       <c r="CW44" t="n">
         <v>18</v>
@@ -30028,7 +30028,7 @@
         <v>21.9</v>
       </c>
       <c r="J45" t="n">
-        <v>13.3</v>
+        <v>39.7</v>
       </c>
       <c r="K45" t="n">
         <v>28.1</v>
@@ -30109,7 +30109,7 @@
         <v>22.5</v>
       </c>
       <c r="AK45" t="n">
-        <v>11.6</v>
+        <v>30.9</v>
       </c>
       <c r="AL45" t="n">
         <v>22.6</v>
@@ -30136,10 +30136,10 @@
         <v>23.4</v>
       </c>
       <c r="AT45" t="n">
-        <v>12.1</v>
+        <v>45.8</v>
       </c>
       <c r="AU45" t="n">
-        <v>14.3</v>
+        <v>37.3</v>
       </c>
       <c r="AV45" t="n">
         <v>19.7</v>
@@ -30169,7 +30169,7 @@
         <v>24.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>13.2</v>
+        <v>44.4</v>
       </c>
       <c r="BF45" t="n">
         <v>27.2</v>
@@ -30271,7 +30271,7 @@
         <v>20.8</v>
       </c>
       <c r="CM45" t="n">
-        <v>15.5</v>
+        <v>50.9</v>
       </c>
       <c r="CN45" t="n">
         <v>25.9</v>
@@ -30618,304 +30618,304 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9.1</v>
+        <v>51.1</v>
       </c>
       <c r="C47" t="n">
-        <v>9.699999999999999</v>
+        <v>34.5</v>
       </c>
       <c r="D47" t="n">
-        <v>6.5</v>
+        <v>38.7</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>48.4</v>
       </c>
       <c r="F47" t="n">
-        <v>3.4</v>
+        <v>46.3</v>
       </c>
       <c r="G47" t="n">
-        <v>0.6</v>
+        <v>33.6</v>
       </c>
       <c r="H47" t="n">
-        <v>4.6</v>
+        <v>48.9</v>
       </c>
       <c r="I47" t="n">
-        <v>6.9</v>
+        <v>43.3</v>
       </c>
       <c r="J47" t="n">
-        <v>3.9</v>
+        <v>48.4</v>
       </c>
       <c r="K47" t="n">
-        <v>7.7</v>
+        <v>43.4</v>
       </c>
       <c r="L47" t="n">
-        <v>6.1</v>
+        <v>47.6</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>46.8</v>
       </c>
       <c r="N47" t="n">
-        <v>7</v>
+        <v>39.1</v>
       </c>
       <c r="O47" t="n">
-        <v>5.3</v>
+        <v>22.1</v>
       </c>
       <c r="P47" t="n">
-        <v>3.7</v>
+        <v>47.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.4</v>
+        <v>46.1</v>
       </c>
       <c r="R47" t="n">
-        <v>9</v>
+        <v>47.1</v>
       </c>
       <c r="S47" t="n">
-        <v>3.1</v>
+        <v>60.1</v>
       </c>
       <c r="T47" t="n">
-        <v>7.3</v>
+        <v>43.6</v>
       </c>
       <c r="U47" t="n">
-        <v>11.2</v>
+        <v>43.5</v>
       </c>
       <c r="V47" t="n">
-        <v>6.9</v>
+        <v>36.7</v>
       </c>
       <c r="W47" t="n">
-        <v>11.7</v>
+        <v>48.3</v>
       </c>
       <c r="X47" t="n">
-        <v>9.4</v>
+        <v>42.7</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.5</v>
+        <v>40.9</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.6</v>
+        <v>32.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>11.1</v>
+        <v>36.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>10.8</v>
+        <v>38.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>5.8</v>
+        <v>53.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>3</v>
+        <v>43.3</v>
       </c>
       <c r="AE47" t="n">
-        <v>10.8</v>
+        <v>38.6</v>
       </c>
       <c r="AF47" t="n">
-        <v>10.1</v>
+        <v>44.6</v>
       </c>
       <c r="AG47" t="n">
-        <v>4.2</v>
+        <v>42.1</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.9</v>
+        <v>38.2</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.9</v>
+        <v>25.5</v>
       </c>
       <c r="AJ47" t="n">
-        <v>11.9</v>
+        <v>37.9</v>
       </c>
       <c r="AK47" t="n">
-        <v>5.2</v>
+        <v>43</v>
       </c>
       <c r="AL47" t="n">
-        <v>3.4</v>
+        <v>39.8</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.7</v>
+        <v>40.9</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.7</v>
+        <v>34.2</v>
       </c>
       <c r="AO47" t="n">
-        <v>11.4</v>
+        <v>51.2</v>
       </c>
       <c r="AP47" t="n">
-        <v>12.5</v>
+        <v>29.8</v>
       </c>
       <c r="AQ47" t="n">
-        <v>15.4</v>
+        <v>46.3</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.3</v>
+        <v>39.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>6.1</v>
+        <v>49.8</v>
       </c>
       <c r="AT47" t="n">
-        <v>4.8</v>
+        <v>47.2</v>
       </c>
       <c r="AU47" t="n">
-        <v>8.800000000000001</v>
+        <v>42.1</v>
       </c>
       <c r="AV47" t="n">
-        <v>4.8</v>
+        <v>50.8</v>
       </c>
       <c r="AW47" t="n">
-        <v>8.6</v>
+        <v>42.4</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.1</v>
+        <v>34.5</v>
       </c>
       <c r="AY47" t="n">
-        <v>3.9</v>
+        <v>20.9</v>
       </c>
       <c r="AZ47" t="n">
-        <v>11</v>
+        <v>32.6</v>
       </c>
       <c r="BA47" t="n">
-        <v>8.800000000000001</v>
+        <v>37.8</v>
       </c>
       <c r="BB47" t="n">
-        <v>0.3</v>
+        <v>45.2</v>
       </c>
       <c r="BC47" t="n">
-        <v>9.300000000000001</v>
+        <v>37</v>
       </c>
       <c r="BD47" t="n">
-        <v>7.1</v>
+        <v>40</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.199999999999999</v>
+        <v>46.6</v>
       </c>
       <c r="BF47" t="n">
-        <v>4</v>
+        <v>48.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>8.5</v>
+        <v>43.1</v>
       </c>
       <c r="BH47" t="n">
-        <v>12.6</v>
+        <v>62.7</v>
       </c>
       <c r="BI47" t="n">
-        <v>1.4</v>
+        <v>32.2</v>
       </c>
       <c r="BJ47" t="n">
-        <v>11.5</v>
+        <v>31.9</v>
       </c>
       <c r="BK47" t="n">
-        <v>5.8</v>
+        <v>34.3</v>
       </c>
       <c r="BL47" t="n">
-        <v>1.3</v>
+        <v>32.8</v>
       </c>
       <c r="BM47" t="n">
-        <v>9.199999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="BN47" t="n">
-        <v>9.300000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>33.6</v>
       </c>
       <c r="BP47" t="n">
-        <v>3.2</v>
+        <v>42.5</v>
       </c>
       <c r="BQ47" t="n">
-        <v>10.1</v>
+        <v>40.1</v>
       </c>
       <c r="BR47" t="n">
-        <v>6.1</v>
+        <v>36.9</v>
       </c>
       <c r="BS47" t="n">
-        <v>7.6</v>
+        <v>45.6</v>
       </c>
       <c r="BT47" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="BU47" t="n">
-        <v>7.4</v>
+        <v>41</v>
       </c>
       <c r="BV47" t="n">
-        <v>5.2</v>
+        <v>55.1</v>
       </c>
       <c r="BW47" t="n">
-        <v>7.5</v>
+        <v>56.8</v>
       </c>
       <c r="BX47" t="n">
-        <v>4.1</v>
+        <v>28.2</v>
       </c>
       <c r="BY47" t="n">
-        <v>11.5</v>
+        <v>40.8</v>
       </c>
       <c r="BZ47" t="n">
-        <v>7.9</v>
+        <v>37.7</v>
       </c>
       <c r="CA47" t="n">
-        <v>9.800000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="CB47" t="n">
-        <v>6.3</v>
+        <v>57.2</v>
       </c>
       <c r="CC47" t="n">
-        <v>7.3</v>
+        <v>40.2</v>
       </c>
       <c r="CD47" t="n">
-        <v>10.1</v>
+        <v>41.1</v>
       </c>
       <c r="CE47" t="n">
-        <v>7.7</v>
+        <v>46.3</v>
       </c>
       <c r="CF47" t="n">
-        <v>4.2</v>
+        <v>48.3</v>
       </c>
       <c r="CG47" t="n">
-        <v>7.4</v>
+        <v>49.5</v>
       </c>
       <c r="CH47" t="n">
-        <v>6.8</v>
+        <v>38.3</v>
       </c>
       <c r="CI47" t="n">
-        <v>2.5</v>
+        <v>52.7</v>
       </c>
       <c r="CJ47" t="n">
-        <v>6.5</v>
+        <v>57.5</v>
       </c>
       <c r="CK47" t="n">
-        <v>9.9</v>
+        <v>43.5</v>
       </c>
       <c r="CL47" t="n">
-        <v>7.8</v>
+        <v>31.9</v>
       </c>
       <c r="CM47" t="n">
-        <v>7</v>
+        <v>58.2</v>
       </c>
       <c r="CN47" t="n">
-        <v>5.7</v>
+        <v>49.4</v>
       </c>
       <c r="CO47" t="n">
-        <v>8.1</v>
+        <v>47.9</v>
       </c>
       <c r="CP47" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="CQ47" t="n">
-        <v>7.8</v>
+        <v>36.9</v>
       </c>
       <c r="CR47" t="n">
         <v>11.6</v>
       </c>
       <c r="CS47" t="n">
-        <v>7</v>
+        <v>39.9</v>
       </c>
       <c r="CT47" t="n">
-        <v>3.6</v>
+        <v>42.1</v>
       </c>
       <c r="CU47" t="n">
-        <v>2.8</v>
+        <v>51.5</v>
       </c>
       <c r="CV47" t="n">
-        <v>12.8</v>
+        <v>51.7</v>
       </c>
       <c r="CW47" t="n">
-        <v>9.300000000000001</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="48">
@@ -30985,7 +30985,7 @@
         <v>23.6</v>
       </c>
       <c r="V48" t="n">
-        <v>16.2</v>
+        <v>59.7</v>
       </c>
       <c r="W48" t="n">
         <v>24.4</v>
@@ -30997,7 +30997,7 @@
         <v>17.9</v>
       </c>
       <c r="Z48" t="n">
-        <v>17.8</v>
+        <v>55.2</v>
       </c>
       <c r="AA48" t="n">
         <v>20.8</v>
@@ -31030,7 +31030,7 @@
         <v>27.1</v>
       </c>
       <c r="AK48" t="n">
-        <v>15.4</v>
+        <v>53.6</v>
       </c>
       <c r="AL48" t="n">
         <v>23.5</v>
@@ -31057,7 +31057,7 @@
         <v>20.6</v>
       </c>
       <c r="AT48" t="n">
-        <v>12.2</v>
+        <v>43.4</v>
       </c>
       <c r="AU48" t="n">
         <v>29.4</v>
@@ -31906,7 +31906,7 @@
         <v>26.6</v>
       </c>
       <c r="V51" t="n">
-        <v>11.6</v>
+        <v>34.5</v>
       </c>
       <c r="W51" t="n">
         <v>21</v>
@@ -32038,7 +32038,7 @@
         <v>17.8</v>
       </c>
       <c r="BN51" t="n">
-        <v>11.1</v>
+        <v>39.2</v>
       </c>
       <c r="BO51" t="n">
         <v>24.9</v>
@@ -32089,7 +32089,7 @@
         <v>17.1</v>
       </c>
       <c r="CE51" t="n">
-        <v>10.6</v>
+        <v>41.6</v>
       </c>
       <c r="CF51" t="n">
         <v>17.8</v>
